--- a/admission_checklist_forms/050_long_term_stay_admission_form--admission_checklist_forms.xlsx
+++ b/admission_checklist_forms/050_long_term_stay_admission_form--admission_checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>long_term_stay_applications</t>
+          <t>applicant_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Long Term Stay Applications</t>
+          <t>Applicant Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,25 +543,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>applicant_info</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Applicant Info</t>
+          <t>Emergency Contact</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>emergency_contact</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emergency Contact</t>
+          <t>Medical Conditions</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>medication_list</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medication List</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>medication_dosage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medical Conditions</t>
+          <t>Medication Dosage</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_allergies</t>
+          <t>social_security</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medical Allergies</t>
+          <t>Social Security Number</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medication_list</t>
+          <t>emergency_contact_relationship</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Medication List</t>
+          <t>Emergency Contact Relationship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medication_dosage</t>
+          <t>medical_provider</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Medication Dosage</t>
+          <t>Medical Provider</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>social_security</t>
+          <t>medical_provider_address</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Social Security Number</t>
+          <t>Medical Provider Address</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship</t>
+          <t>medical_record_number</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Emergency Contact Relationship</t>
+          <t>Medical Record Number</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>medical_provider</t>
+          <t>medical_record_provider</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Medical Provider</t>
+          <t>Medical Record Provider</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>medical_provider_address</t>
+          <t>medical_record_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Medical Provider Address</t>
+          <t>Medical Record Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>medical_record_number</t>
+          <t>medical_history</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medical Record Number</t>
+          <t>Medical History</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medical_record_provider</t>
+          <t>medical_allergies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medical Record Provider</t>
+          <t>Medical Allergies</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>medical_record_date</t>
+          <t>medical_conditions_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medical Record Date</t>
+          <t>Medical Conditions 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>medical_record_number</t>
+          <t>emergency_contact_info</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Medical Record Number</t>
+          <t>Emergency Contact Information</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>medication_list</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medication List</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>medication_dosage</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Medication Dosage</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>social_security</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Social Security Number</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Emergency Contact Relationship</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>medical_provider</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Medical Provider</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>medical_provider_address</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Medical Provider Address</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>medical_record_number</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Medical Record Number</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>medical_record_provider</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Medical Record Provider</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1101,9 +940,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>long_term_stay_applications_choices</t>
+          <t>medical_clearance_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>long_term_stay_applications_choices</t>
+          <t>medical_clearance_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,34 +999,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>hypertension</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Hypertension</t>
         </is>
       </c>
     </row>
@@ -1199,29 +1038,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medication_dosage_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1233,63 +1072,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>medication_dosage_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>medication_dosage_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>hypertension</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Hypertension</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>medication_dosage_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
